--- a/data/trans_orig/P16A05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A05-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30263</t>
+          <t>30591</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14803</t>
+          <t>14998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34077</t>
+          <t>32954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30295</t>
+          <t>31017</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56242</t>
+          <t>56736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662731</t>
+          <t>662403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>680033</t>
+          <t>680436</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>654274</t>
+          <t>655397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>673548</t>
+          <t>673353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1325103</t>
+          <t>1324609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1351050</t>
+          <t>1350328</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15400</t>
+          <t>15305</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35814</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41547</t>
+          <t>40976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71020</t>
+          <t>71366</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63676</t>
+          <t>64510</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>98357</t>
+          <t>100178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>925986</t>
+          <t>925987</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>946400</t>
+          <t>946495</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>897373</t>
+          <t>897027</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>926846</t>
+          <t>927417</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1831836</t>
+          <t>1830015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1866517</t>
+          <t>1865683</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21731</t>
+          <t>21897</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35200</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60212</t>
+          <t>60065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47399</t>
+          <t>46176</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78301</t>
+          <t>75925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656778</t>
+          <t>656612</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>671149</t>
+          <t>671187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>623629</t>
+          <t>623776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>648641</t>
+          <t>647985</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1284049</t>
+          <t>1286425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1314951</t>
+          <t>1316174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>17057</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38804</t>
+          <t>37129</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41934</t>
+          <t>42316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72873</t>
+          <t>71684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65859</t>
+          <t>66422</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101218</t>
+          <t>101954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>903418</t>
+          <t>905093</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923913</t>
+          <t>925165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>965739</t>
+          <t>966928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>996678</t>
+          <t>996296</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1879616</t>
+          <t>1878880</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914975</t>
+          <t>1914412</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68210</t>
+          <t>67807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>105061</t>
+          <t>103312</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155861</t>
+          <t>155481</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207406</t>
+          <t>207452</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235596</t>
+          <t>233080</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>301929</t>
+          <t>297133</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3170464</t>
+          <t>3172213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3207315</t>
+          <t>3207718</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3171791</t>
+          <t>3171745</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3223336</t>
+          <t>3223716</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6352793</t>
+          <t>6357589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6419126</t>
+          <t>6421642</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2012 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15413</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36080</t>
+          <t>36543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36449</t>
+          <t>37088</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62959</t>
+          <t>63435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57541</t>
+          <t>57618</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94855</t>
+          <t>90454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664684</t>
+          <t>664221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>685351</t>
+          <t>686102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>629378</t>
+          <t>628902</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655888</t>
+          <t>655249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1298245</t>
+          <t>1302646</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1335559</t>
+          <t>1335482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20393</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43405</t>
+          <t>43430</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64539</t>
+          <t>67181</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101811</t>
+          <t>103981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92598</t>
+          <t>93008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134887</t>
+          <t>135726</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>974542</t>
+          <t>974517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>997554</t>
+          <t>997612</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>927114</t>
+          <t>924944</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>964386</t>
+          <t>961744</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1911985</t>
+          <t>1911146</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1954274</t>
+          <t>1953864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14268</t>
+          <t>14804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>38831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34346</t>
+          <t>33560</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62447</t>
+          <t>60855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54109</t>
+          <t>54878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89915</t>
+          <t>92666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717255</t>
+          <t>717707</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>742270</t>
+          <t>741734</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>713836</t>
+          <t>715428</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>741937</t>
+          <t>742723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1442906</t>
+          <t>1440155</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1478712</t>
+          <t>1477943</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23874</t>
+          <t>23199</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>49232</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57227</t>
+          <t>58215</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91607</t>
+          <t>91993</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91965</t>
+          <t>90215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133414</t>
+          <t>132786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>894432</t>
+          <t>896698</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922056</t>
+          <t>922731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>958139</t>
+          <t>957753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>992519</t>
+          <t>991531</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1862263</t>
+          <t>1862891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1903712</t>
+          <t>1905462</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92671</t>
+          <t>94380</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137543</t>
+          <t>141186</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>225291</t>
+          <t>220617</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>283634</t>
+          <t>285627</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>329798</t>
+          <t>329289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>410502</t>
+          <t>410329</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3283636</t>
+          <t>3279993</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3328508</t>
+          <t>3326799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3263658</t>
+          <t>3261665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3322001</t>
+          <t>3326675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6557969</t>
+          <t>6558142</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6638673</t>
+          <t>6639182</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25575</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39376</t>
+          <t>40757</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66657</t>
+          <t>67411</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54211</t>
+          <t>52800</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85726</t>
+          <t>85534</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649225</t>
+          <t>649007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>665079</t>
+          <t>664865</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>606182</t>
+          <t>605428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>633463</t>
+          <t>632082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1261913</t>
+          <t>1262105</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1293428</t>
+          <t>1294839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,08%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>43811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54324</t>
+          <t>53395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>87775</t>
+          <t>88545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>81271</t>
+          <t>82172</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122348</t>
+          <t>123027</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>979602</t>
+          <t>978620</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1000510</t>
+          <t>1001106</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>955138</t>
+          <t>954368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>988589</t>
+          <t>989518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1942996</t>
+          <t>1942317</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1984073</t>
+          <t>1983172</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20057</t>
+          <t>20449</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41699</t>
+          <t>42802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44138</t>
+          <t>44112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73638</t>
+          <t>73893</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71283</t>
+          <t>69815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106591</t>
+          <t>108467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717853</t>
+          <t>716750</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>739495</t>
+          <t>739103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>711373</t>
+          <t>711118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>740873</t>
+          <t>740899</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1437972</t>
+          <t>1436096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1473280</t>
+          <t>1474748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29083</t>
+          <t>29050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52751</t>
+          <t>55196</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72822</t>
+          <t>71842</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112441</t>
+          <t>110848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108665</t>
+          <t>109481</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155479</t>
+          <t>155511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>884816</t>
+          <t>882371</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>908484</t>
+          <t>908517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>931338</t>
+          <t>932931</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>970957</t>
+          <t>971937</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1825867</t>
+          <t>1825835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1872681</t>
+          <t>1871865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>100365</t>
+          <t>97572</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>144005</t>
+          <t>140507</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>238343</t>
+          <t>240366</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>303133</t>
+          <t>304472</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>348475</t>
+          <t>350080</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>426976</t>
+          <t>429092</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3250345</t>
+          <t>3253843</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3293985</t>
+          <t>3296778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3241409</t>
+          <t>3240070</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3306199</t>
+          <t>3304176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6511916</t>
+          <t>6509800</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6590417</t>
+          <t>6588812</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>39108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39189</t>
+          <t>39965</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58927</t>
+          <t>59136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>63448</t>
+          <t>64368</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90948</t>
+          <t>90416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>596600</t>
+          <t>595843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>615637</t>
+          <t>614592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>616495</t>
+          <t>616286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>636233</t>
+          <t>635457</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1219425</t>
+          <t>1219957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1246925</t>
+          <t>1246005</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47312</t>
+          <t>47910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84876</t>
+          <t>84446</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113485</t>
+          <t>113521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90512</t>
+          <t>87583</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155328</t>
+          <t>155634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1145552</t>
+          <t>1144954</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1176581</t>
+          <t>1177457</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>844621</t>
+          <t>844585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>873230</t>
+          <t>873660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1995643</t>
+          <t>1995337</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2060459</t>
+          <t>2063388</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47592</t>
+          <t>48213</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>27488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75724</t>
+          <t>77418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60745</t>
+          <t>58647</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111943</t>
+          <t>113049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656092</t>
+          <t>655471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679719</t>
+          <t>678936</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>856458</t>
+          <t>854764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>904580</t>
+          <t>904694</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1523923</t>
+          <t>1522817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1575121</t>
+          <t>1577219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36608</t>
+          <t>35345</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>60305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68618</t>
+          <t>67381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109869</t>
+          <t>109994</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114078</t>
+          <t>115011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160275</t>
+          <t>160734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>865520</t>
+          <t>866526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>890223</t>
+          <t>891486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>981505</t>
+          <t>981380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1022756</t>
+          <t>1023993</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857930</t>
+          <t>1857471</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1904127</t>
+          <t>1903194</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111138</t>
+          <t>114257</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169391</t>
+          <t>169604</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>231360</t>
+          <t>240418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>325044</t>
+          <t>327373</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>376179</t>
+          <t>373970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>481945</t>
+          <t>479385</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3288939</t>
+          <t>3288726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3347192</t>
+          <t>3344073</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3332040</t>
+          <t>3329711</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3425724</t>
+          <t>3416666</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6633469</t>
+          <t>6636029</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6739235</t>
+          <t>6741444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P16A05-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>13108</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30591</t>
+          <t>30428</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>14627</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>33757</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31017</t>
+          <t>32417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56736</t>
+          <t>56774</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>662403</t>
+          <t>662566</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>680436</t>
+          <t>679886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>655397</t>
+          <t>654594</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>673353</t>
+          <t>673724</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1324609</t>
+          <t>1324571</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1350328</t>
+          <t>1348928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>15478</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35813</t>
+          <t>36049</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40976</t>
+          <t>42800</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71366</t>
+          <t>73421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64510</t>
+          <t>63754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100178</t>
+          <t>99700</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>925987</t>
+          <t>925751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>946495</t>
+          <t>946322</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>897027</t>
+          <t>894972</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>927417</t>
+          <t>925593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1830015</t>
+          <t>1830493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1865683</t>
+          <t>1866439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21897</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35856</t>
+          <t>35612</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60065</t>
+          <t>60752</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46176</t>
+          <t>46751</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75925</t>
+          <t>74971</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656612</t>
+          <t>656574</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>671187</t>
+          <t>670781</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>623776</t>
+          <t>623089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647985</t>
+          <t>648229</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1286425</t>
+          <t>1287379</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1316174</t>
+          <t>1315599</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37129</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42316</t>
+          <t>41849</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71684</t>
+          <t>69717</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66422</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101954</t>
+          <t>103533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>905093</t>
+          <t>903078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>925165</t>
+          <t>923895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>966928</t>
+          <t>968895</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>996296</t>
+          <t>996763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1878880</t>
+          <t>1877301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914412</t>
+          <t>1913101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67807</t>
+          <t>69233</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103312</t>
+          <t>104896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>155481</t>
+          <t>153029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207452</t>
+          <t>205573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>233080</t>
+          <t>232017</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>297133</t>
+          <t>294823</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3172213</t>
+          <t>3170629</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3207718</t>
+          <t>3206292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3171745</t>
+          <t>3173624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3223716</t>
+          <t>3226168</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6357589</t>
+          <t>6359899</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6421642</t>
+          <t>6422705</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>15041</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36543</t>
+          <t>35612</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37088</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63435</t>
+          <t>64209</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57618</t>
+          <t>57627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>93626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664221</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>686102</t>
+          <t>685723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>628902</t>
+          <t>628128</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>655249</t>
+          <t>655772</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1302646</t>
+          <t>1299474</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1335482</t>
+          <t>1335473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>20334</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43430</t>
+          <t>41912</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67181</t>
+          <t>66753</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>103981</t>
+          <t>101559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>93008</t>
+          <t>91300</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>135726</t>
+          <t>134944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>974517</t>
+          <t>976035</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>997612</t>
+          <t>997613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>924944</t>
+          <t>927366</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>961744</t>
+          <t>962172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1911146</t>
+          <t>1911928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1953864</t>
+          <t>1955572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14804</t>
+          <t>14666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38831</t>
+          <t>40582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33560</t>
+          <t>33853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60855</t>
+          <t>64199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54878</t>
+          <t>53343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92666</t>
+          <t>91857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>717707</t>
+          <t>715956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>741734</t>
+          <t>741872</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>715428</t>
+          <t>712084</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>742723</t>
+          <t>742430</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1440155</t>
+          <t>1440964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1477943</t>
+          <t>1479478</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23199</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49232</t>
+          <t>50406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58215</t>
+          <t>59136</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>91993</t>
+          <t>91964</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90215</t>
+          <t>89319</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132786</t>
+          <t>132670</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>896698</t>
+          <t>895524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>922731</t>
+          <t>922229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>957753</t>
+          <t>957782</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>991531</t>
+          <t>990610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1862891</t>
+          <t>1863007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1905462</t>
+          <t>1906358</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94380</t>
+          <t>91134</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141186</t>
+          <t>138415</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>220617</t>
+          <t>222140</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>285627</t>
+          <t>287276</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>329289</t>
+          <t>330772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>410329</t>
+          <t>412982</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3279993</t>
+          <t>3282764</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3326799</t>
+          <t>3330045</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3261665</t>
+          <t>3260016</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3326675</t>
+          <t>3325152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6558142</t>
+          <t>6555489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6639182</t>
+          <t>6637699</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>25117</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40757</t>
+          <t>39306</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67411</t>
+          <t>66226</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52800</t>
+          <t>54278</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85534</t>
+          <t>87502</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>649007</t>
+          <t>649683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>664865</t>
+          <t>665731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>605428</t>
+          <t>606613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>632082</t>
+          <t>633533</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1262105</t>
+          <t>1260137</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1294839</t>
+          <t>1293361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>21746</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43811</t>
+          <t>45798</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>53395</t>
+          <t>53653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>88545</t>
+          <t>87595</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82172</t>
+          <t>81501</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123027</t>
+          <t>124545</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>978620</t>
+          <t>976633</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1001106</t>
+          <t>1000685</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>954368</t>
+          <t>955318</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>989518</t>
+          <t>989260</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1942317</t>
+          <t>1940799</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1983172</t>
+          <t>1983843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20449</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42802</t>
+          <t>43073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44112</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73893</t>
+          <t>73781</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69815</t>
+          <t>71244</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108467</t>
+          <t>107807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>716750</t>
+          <t>716479</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>739103</t>
+          <t>739362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>711118</t>
+          <t>711230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>740899</t>
+          <t>741458</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1436096</t>
+          <t>1436756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1474748</t>
+          <t>1473319</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>29578</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55196</t>
+          <t>54862</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71842</t>
+          <t>74002</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110848</t>
+          <t>111479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109481</t>
+          <t>110283</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155511</t>
+          <t>154958</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>882371</t>
+          <t>882705</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>908517</t>
+          <t>907989</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>932931</t>
+          <t>932300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>971937</t>
+          <t>969777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1825835</t>
+          <t>1826388</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1871865</t>
+          <t>1871063</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97572</t>
+          <t>99860</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140507</t>
+          <t>142104</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>240366</t>
+          <t>240175</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>304472</t>
+          <t>304450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>350080</t>
+          <t>347022</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>429092</t>
+          <t>426620</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3253843</t>
+          <t>3252246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3296778</t>
+          <t>3294490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3240070</t>
+          <t>3240092</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3304176</t>
+          <t>3304367</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6509800</t>
+          <t>6512272</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6588812</t>
+          <t>6591870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28116</t>
+          <t>30859</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20359</t>
+          <t>21075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39108</t>
+          <t>42973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>52209</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39965</t>
+          <t>42459</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59136</t>
+          <t>62796</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>76876</t>
+          <t>83068</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64368</t>
+          <t>68453</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90416</t>
+          <t>99187</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>606835</t>
+          <t>659356</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>595843</t>
+          <t>647242</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>614592</t>
+          <t>669140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>626661</t>
+          <t>680573</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>616286</t>
+          <t>669986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>635457</t>
+          <t>690323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1233497</t>
+          <t>1339929</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1219957</t>
+          <t>1323810</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1246005</t>
+          <t>1354544</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634951</t>
+          <t>690215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675422</t>
+          <t>732782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310373</t>
+          <t>1422997</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31660</t>
+          <t>32915</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>22922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47910</t>
+          <t>45164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98922</t>
+          <t>108458</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84446</t>
+          <t>93215</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113521</t>
+          <t>125613</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>130582</t>
+          <t>141373</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87583</t>
+          <t>121635</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155634</t>
+          <t>161613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1161204</t>
+          <t>1016002</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1144954</t>
+          <t>1003753</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1177457</t>
+          <t>1025995</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>859184</t>
+          <t>962380</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>844585</t>
+          <t>945225</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>873660</t>
+          <t>977623</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2020389</t>
+          <t>1978382</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1995337</t>
+          <t>1958142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2063388</t>
+          <t>1998120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35069</t>
+          <t>39319</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24748</t>
+          <t>28828</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48213</t>
+          <t>53400</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>54539</t>
+          <t>59898</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27488</t>
+          <t>47275</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77418</t>
+          <t>72922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>89608</t>
+          <t>99217</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58647</t>
+          <t>82962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113049</t>
+          <t>118150</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>668615</t>
+          <t>762767</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655471</t>
+          <t>748686</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678936</t>
+          <t>773258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>877643</t>
+          <t>751087</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>854764</t>
+          <t>738063</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>904694</t>
+          <t>763710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1546258</t>
+          <t>1513853</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1522817</t>
+          <t>1494920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1577219</t>
+          <t>1530108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932182</t>
+          <t>810985</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932182</t>
+          <t>810985</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932182</t>
+          <t>810985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1635866</t>
+          <t>1613070</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1635866</t>
+          <t>1613070</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1635866</t>
+          <t>1613070</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>46870</t>
+          <t>47347</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35345</t>
+          <t>36386</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60305</t>
+          <t>62049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>88664</t>
+          <t>93522</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67381</t>
+          <t>79423</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109994</t>
+          <t>109240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>135534</t>
+          <t>140869</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>115011</t>
+          <t>123356</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>160734</t>
+          <t>163332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>879961</t>
+          <t>942715</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>866526</t>
+          <t>928013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>891486</t>
+          <t>953676</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1002710</t>
+          <t>1023509</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>981380</t>
+          <t>1007791</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1023993</t>
+          <t>1037608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1882671</t>
+          <t>1966224</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1857471</t>
+          <t>1943761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1903194</t>
+          <t>1983737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091374</t>
+          <t>1117031</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018205</t>
+          <t>2107093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>141714</t>
+          <t>150440</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114257</t>
+          <t>128724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>169604</t>
+          <t>176451</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>290887</t>
+          <t>314087</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>240418</t>
+          <t>288698</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>327373</t>
+          <t>344031</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>432601</t>
+          <t>464527</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>373970</t>
+          <t>428107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>479385</t>
+          <t>501395</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3316616</t>
+          <t>3380840</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3288726</t>
+          <t>3354829</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3344073</t>
+          <t>3402556</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3366197</t>
+          <t>3417548</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3329711</t>
+          <t>3387604</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3416666</t>
+          <t>3442937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6682813</t>
+          <t>6798388</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6636029</t>
+          <t>6761520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6741444</t>
+          <t>6834808</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657084</t>
+          <t>3731635</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657084</t>
+          <t>3731635</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657084</t>
+          <t>3731635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7115414</t>
+          <t>7262915</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7115414</t>
+          <t>7262915</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7115414</t>
+          <t>7262915</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
